--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -483,7 +483,7 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -550,9 +550,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>A
-OBA
-BG_ISL 2026-27</t>
+          <t>A\nOBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1371,7 +1369,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -1384,7 +1382,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1430,9 +1428,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>A
-OBA
-BG_ISL 2026-27</t>
+          <t>A\nOBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2190,7 +2186,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -2203,7 +2199,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2249,9 +2245,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>A
-OBA
-BG_ISL 2026-27</t>
+          <t>A\nOBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1382,7 +1382,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2199,7 +2199,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 17." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -2643,7 +2643,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 05.09.2026</t>
+          <t>Open Line FR Report - As On 17.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2733,19 +2733,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,992
-Cr. 7.80</t>
+          <t>81,555
+Cr. 8.16</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-82,911
-Cr. -8.29</t>
+          <t>-79,348
+Cr. -7.93</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2773,19 +2773,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>11,801
-Cr. 1.18</t>
+          <t>12,549
+Cr. 1.25</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-20,426
-Cr. -2.04</t>
+          <t>-19,678
+Cr. -1.97</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57,289
-Cr. 5.73</t>
+          <t>64,226
+Cr. 6.42</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-63,029
-Cr. -6.30</t>
+          <t>-56,092
+Cr. -5.61</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2853,19 +2853,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>363,937
-Cr. 36.39</t>
+          <t>376,586
+Cr. 37.66</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-143,483
-Cr. -14.35</t>
+          <t>-130,834
+Cr. -13.08</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>74.22</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2893,19 +2893,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,692,699
-Cr. 369.27</t>
+          <t>3,758,184
+Cr. 375.82</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>729,904
-Cr. 72.99</t>
+          <t>795,389
+Cr. 79.54</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>124.64</t>
+          <t>126.85</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2933,19 +2933,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>151,197
-Cr. 15.12</t>
+          <t>164,242
+Cr. 16.42</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>18,930
-Cr. 1.89</t>
+          <t>31,975
+Cr. 3.20</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>114.31</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2973,19 +2973,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>123,038
-Cr. 12.30</t>
+          <t>139,533
+Cr. 13.95</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-399,805
-Cr. -39.98</t>
+          <t>-383,310
+Cr. -38.33</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3013,19 +3013,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>94,924
-Cr. 9.49</t>
+          <t>104,326
+Cr. 10.43</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-212,919
-Cr. -21.29</t>
+          <t>-203,517
+Cr. -20.35</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>33.89</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5,129
-Cr. 0.51</t>
+          <t>5,681
+Cr. 0.57</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-48,573
-Cr. -4.86</t>
+          <t>-48,021
+Cr. -4.80</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3213,19 +3213,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>131,048
-Cr. 13.10</t>
+          <t>139,726
+Cr. 13.97</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-179,864
-Cr. -17.99</t>
+          <t>-171,186
+Cr. -17.12</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>44.94</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3293,19 +3293,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>103,375
-Cr. 10.34</t>
+          <t>112,585
+Cr. 11.26</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-212,358
-Cr. -21.24</t>
+          <t>-203,148
+Cr. -20.31</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3405,19 +3405,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,896,554
-Cr. 489.66</t>
+          <t>5,043,318
+Cr. 504.33</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-711,147
-Cr. -71.11</t>
+          <t>-564,383
+Cr. -56.44</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 17.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3538,24 +3538,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>408,842
-Cr. 40.88</t>
+          <t>441,204
+Cr. 44.12</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>609,511
-Cr. 60.95</t>
+          <t>577,149
+Cr. 57.71</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3698,24 +3698,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,746,106
-Cr. 374.61</t>
+          <t>3,802,846
+Cr. 380.28</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-628,591
-Cr. -62.86</t>
+          <t>-685,331
+Cr. -68.53</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>121.98</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-21.98</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>707,656
-Cr. 70.77</t>
+          <t>765,318
+Cr. 76.53</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>593,353
-Cr. 59.34</t>
+          <t>535,691
+Cr. 53.57</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 17." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1382,7 +1382,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2199,7 +2199,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2643,7 +2643,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 17.09.2026</t>
+          <t>Open Line FR Report - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2733,19 +2733,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>81,555
-Cr. 8.16</t>
+          <t>77,992
+Cr. 7.80</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-79,348
-Cr. -7.93</t>
+          <t>-82,911
+Cr. -8.29</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2773,19 +2773,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>12,549
-Cr. 1.25</t>
+          <t>11,801
+Cr. 1.18</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-19,678
-Cr. -1.97</t>
+          <t>-20,426
+Cr. -2.04</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>64,226
-Cr. 6.42</t>
+          <t>57,289
+Cr. 5.73</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-56,092
-Cr. -5.61</t>
+          <t>-63,029
+Cr. -6.30</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2853,19 +2853,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>376,586
-Cr. 37.66</t>
+          <t>363,937
+Cr. 36.39</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-130,834
-Cr. -13.08</t>
+          <t>-143,483
+Cr. -14.35</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>74.22</t>
+          <t>71.72</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2893,19 +2893,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,758,184
-Cr. 375.82</t>
+          <t>3,692,699
+Cr. 369.27</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>795,389
-Cr. 79.54</t>
+          <t>729,904
+Cr. 72.99</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>126.85</t>
+          <t>124.64</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2933,19 +2933,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>164,242
-Cr. 16.42</t>
+          <t>151,197
+Cr. 15.12</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>31,975
-Cr. 3.20</t>
+          <t>18,930
+Cr. 1.89</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>114.31</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2973,19 +2973,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>139,533
-Cr. 13.95</t>
+          <t>123,038
+Cr. 12.30</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-383,310
-Cr. -38.33</t>
+          <t>-399,805
+Cr. -39.98</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3013,19 +3013,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>104,326
-Cr. 10.43</t>
+          <t>94,924
+Cr. 9.49</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-203,517
-Cr. -20.35</t>
+          <t>-212,919
+Cr. -21.29</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5,681
-Cr. 0.57</t>
+          <t>5,129
+Cr. 0.51</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-48,021
-Cr. -4.80</t>
+          <t>-48,573
+Cr. -4.86</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3213,19 +3213,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>139,726
-Cr. 13.97</t>
+          <t>131,048
+Cr. 13.10</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-171,186
-Cr. -17.12</t>
+          <t>-179,864
+Cr. -17.99</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3293,19 +3293,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>112,585
-Cr. 11.26</t>
+          <t>103,375
+Cr. 10.34</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-203,148
-Cr. -20.31</t>
+          <t>-212,358
+Cr. -21.24</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3405,19 +3405,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>5,043,318
-Cr. 504.33</t>
+          <t>4,896,554
+Cr. 489.66</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-564,383
-Cr. -56.44</t>
+          <t>-711,147
+Cr. -71.11</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 17.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3538,24 +3538,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>441,204
-Cr. 44.12</t>
+          <t>408,842
+Cr. 40.88</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>577,149
-Cr. 57.71</t>
+          <t>609,511
+Cr. 60.95</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>59.85</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3698,24 +3698,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,802,846
-Cr. 380.28</t>
+          <t>3,746,106
+Cr. 374.61</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-685,331
-Cr. -68.53</t>
+          <t>-628,591
+Cr. -62.86</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>121.98</t>
+          <t>120.16</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-21.98</t>
+          <t>-20.16</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>765,318
-Cr. 76.53</t>
+          <t>707,656
+Cr. 70.77</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>535,691
-Cr. 53.57</t>
+          <t>593,353
+Cr. 59.34</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>45.61</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-22T17:27:48+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -616,26 +616,94 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>641,522
-Cr. 64.15</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>641,522</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>64.15 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>267,301
-Cr. 26.73</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>267,301</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>26.73 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>294,135
-Cr. 29.41</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>294,135</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>29.41 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>26,834
-Cr. 2.68</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>26,834</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.68 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -645,8 +713,25 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>347,387
-Cr. 34.74</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>347,387</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>34.74 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -656,8 +741,25 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>693,876
-Cr. 69.39</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>693,876</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>69.39 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -674,26 +776,94 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>3,608,902
-Cr. 360.89</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,608,902</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>360.89 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,503,709
-Cr. 150.37</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,503,709</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>150.37 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,781,320
-Cr. 178.13</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,781,320</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>178.13 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>277,611
-Cr. 27.76</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>277,611</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>27.76 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -703,8 +873,25 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1,827,582
-Cr. 182.76</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,827,582</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>182.76 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -714,8 +901,25 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>3,996,057
-Cr. 399.61</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,996,057</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>399.61 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -732,26 +936,94 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1,864,843
-Cr. 186.48</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,864,843</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>186.48 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>777,018
-Cr. 77.70</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>777,018</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>77.70 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>782,032
-Cr. 78.20</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>782,032</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>78.20 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>5,014
-Cr. 0.50</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,014</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.50 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -761,8 +1033,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1,082,811
-Cr. 108.28</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,082,811</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>108.28 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -772,8 +1061,25 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2,000,064
-Cr. 200.01</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,000,064</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>200.01 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -790,26 +1096,94 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>1,353,581
-Cr. 135.36</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,353,581</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>135.36 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>563,992
-Cr. 56.40</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>563,992</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>56.40 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>911,131
-Cr. 91.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>911,131</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>91.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>347,139
-Cr. 34.71</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>347,139</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>34.71 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -819,8 +1193,25 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>442,450
-Cr. 44.24</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>442,450</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>44.24 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -830,8 +1221,25 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>1,511,638
-Cr. 151.16</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,511,638</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>151.16 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -848,26 +1256,94 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2,059,950
-Cr. 206.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,059,950</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>206.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>858,312
-Cr. 85.83</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>858,312</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>85.83 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>995,022
-Cr. 99.50</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>995,022</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>99.50 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>136,710
-Cr. 13.67</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>136,710</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.67 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -877,8 +1353,25 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,064,928
-Cr. 106.49</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,064,928</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>106.49 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -888,8 +1381,25 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2,171,600
-Cr. 217.16</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,171,600</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>217.16 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -906,26 +1416,94 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>3,352,566
-Cr. 335.26</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,352,566</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>335.26 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1,396,902
-Cr. 139.69</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,396,902</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>139.69 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,978,638
-Cr. 197.86</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,978,638</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>197.86 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>581,736
-Cr. 58.17</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>581,736</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>58.17 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -935,8 +1513,25 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,373,928
-Cr. 137.39</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,373,928</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>137.39 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -946,8 +1541,25 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>3,801,767
-Cr. 380.18</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,801,767</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>380.18 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -964,26 +1576,94 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4,428,766
-Cr. 442.88</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>4,428,766</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>442.88 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1,845,319
-Cr. 184.53</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,845,319</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>184.53 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2,192,865
-Cr. 219.29</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,192,865</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>219.29 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>347,546
-Cr. 34.75</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>347,546</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>34.75 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -993,8 +1673,25 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,235,901
-Cr. 223.59</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,235,901</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>223.59 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1004,8 +1701,25 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>4,947,572
-Cr. 494.76</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>4,947,572</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>494.76 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1022,26 +1736,94 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>11,607,206
-Cr. 1160.72</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>11,607,206</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1160.72 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>4,836,336
-Cr. 483.63</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>4,836,336</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>483.63 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>5,702,475
-Cr. 570.25</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,702,475</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>570.25 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>866,139
-Cr. 86.61</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>866,139</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>86.61 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1051,8 +1833,25 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>5,904,731
-Cr. 590.47</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,904,731</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>590.47 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1062,8 +1861,25 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>12,690,658
-Cr. 1269.07</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>12,690,658</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1269.07 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1080,26 +1896,94 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1,392,832
-Cr. 139.28</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,392,832</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>139.28 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>580,347
-Cr. 58.03</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>580,347</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>58.03 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>916,954
-Cr. 91.70</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>916,954</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>91.70 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>336,607
-Cr. 33.66</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>336,607</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.66 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1109,8 +1993,25 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>475,878
-Cr. 47.59</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>475,878</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>47.59 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1120,8 +2021,25 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1,451,556
-Cr. 145.16</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,451,556</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>145.16 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1138,26 +2056,94 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>994,638
-Cr. 99.46</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>994,638</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>99.46 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>414,432
-Cr. 41.44</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>414,432</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>41.44 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>441,761
-Cr. 44.18</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>441,761</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>44.18 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>27,328
-Cr. 2.73</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>27,328</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.73 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1167,8 +2153,25 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>552,877
-Cr. 55.29</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>552,877</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>55.29 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1178,8 +2181,25 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>1,025,571
-Cr. 102.56</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,025,571</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>102.56 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1196,26 +2216,94 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>1,291,067
-Cr. 129.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,291,067</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>129.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>537,945
-Cr. 53.79</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>537,945</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>53.79 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>532,662
-Cr. 53.27</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>532,662</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>53.27 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>-5,283
-Cr. -0.53</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-5,283</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.53 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1225,8 +2313,25 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>758,405
-Cr. 75.84</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>758,405</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>75.84 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1236,8 +2341,25 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1,226,809
-Cr. 122.68</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,226,809</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>122.68 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1250,26 +2372,94 @@
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>32,595,873
-Cr. 3259.59</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>32,595,873</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3259.59 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>13,581,614
-Cr. 1358.16</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>13,581,614</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1358.16 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>16,528,995
-Cr. 1652.90</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>16,528,995</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1652.90 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2,947,381
-Cr. 294.74</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,947,381</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>294.74 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1279,8 +2469,25 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>16,066,878
-Cr. 1606.69</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>16,066,878</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1606.69 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1290,8 +2497,25 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>35,517,168
-Cr. 3551.72</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>35,517,168</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3551.72 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1308,26 +2532,94 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>-13,045
-Cr. -1.30</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-13,045</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.30 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>-5,435
-Cr. -0.54</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-5,435</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.54 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,578,052
-Cr. 157.81</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,578,052</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>157.81 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1,583,487
-Cr. 158.35</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,583,487</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>158.35 Cr</t>
+          </r>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1337,8 +2629,25 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,591,097
-Cr. -159.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-1,591,097</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-159.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1348,8 +2657,25 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-2,031
-Cr. -0.20</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-2,031</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.20 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1370,11 +2696,11 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
@@ -1382,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-22T17:27:48+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1489,48 +2815,150 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>6,706,409
-Cr. 670.64</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>671</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.07 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2,794,337
-Cr. 279.43</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>280</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.03 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3,071,823
-Cr. 307.18</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,071,823</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>307.18 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>277,486
-Cr. 27.75</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,071,543</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>307.15 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>1098715</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>3,634,586
-Cr. 363.46</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-3,071,152</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-307.12 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>457798</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>7,351,228
-Cr. 735.12</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>7,351,228</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>735.12 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1542,48 +2970,150 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>4,100,453
-Cr. 410.05</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>410</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.04 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1,708,522
-Cr. 170.85</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>171</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.02 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,966,618
-Cr. 196.66</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,966,618</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>196.66 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>258,096
-Cr. 25.81</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,966,447</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>196.64 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1151191</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,133,835
-Cr. 213.38</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-1,966,208</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-196.62 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>479663</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>4,447,868
-Cr. 444.79</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>4,447,868</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>444.79 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1595,48 +3125,150 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>285,089
-Cr. 28.51</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>29</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>118,787
-Cr. 11.88</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>12</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>72
-Cr. 0.01</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>72</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-118,715
-Cr. -11.87</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>60</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>285,017
-Cr. 28.50</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-43</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>302,570
-Cr. 30.26</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>302,570</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.26 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1648,48 +3280,150 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>776,198
-Cr. 77.62</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>78</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>323,416
-Cr. 32.34</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>32</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>337,362
-Cr. 33.74</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>337,362</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.74 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>13,946
-Cr. 1.39</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>337,330</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.73 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1038037</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>438,836
-Cr. 43.88</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-337,284</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-33.73 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>432515</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>802,369
-Cr. 80.24</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>802,369</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>80.24 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1701,48 +3435,150 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>496,609
-Cr. 49.66</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>50</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>206,920
-Cr. 20.69</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>21</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>216,397
-Cr. 21.64</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>216,397</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>21.64 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>9,477
-Cr. 0.95</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>216,376</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>21.64 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>1038706</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>280,212
-Cr. 28.02</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-216,347</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.63 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>432794</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>509,846
-Cr. 50.98</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>509,846</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>50.98 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1754,48 +3590,150 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>680,197
-Cr. 68.02</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>68</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>283,415
-Cr. 28.34</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>28</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>364,653
-Cr. 36.47</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>364,653</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.47 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>81,238
-Cr. 8.12</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>364,625</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.46 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1287011</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>315,544
-Cr. 31.55</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-364,585</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-36.46 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>536254</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>764,171
-Cr. 76.42</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>764,171</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>76.42 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1807,48 +3745,150 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>77,300
-Cr. 7.73</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>8</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>32,208
-Cr. 3.22</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>59,582
-Cr. 5.96</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>59,582</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.96 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>27,374
-Cr. 2.74</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>59,579</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.96 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1787460</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>17,718
-Cr. 1.77</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-59,574</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-5.96 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>744775</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>106,223
-Cr. 10.62</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>106,223</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.62 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1860,48 +3900,150 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>209,913
-Cr. 20.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>21</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>87,464
-Cr. 8.75</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>9</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>122,492
-Cr. 12.25</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>122,492</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.25 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>35,028
-Cr. 3.50</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>122,483</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.25 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1399909</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>87,421
-Cr. 8.74</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-122,471</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-12.25 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>583295</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>294,342
-Cr. 29.43</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>294,342</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>29.43 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1913,48 +4055,150 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>527,832
-Cr. 52.78</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>53</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>219,930
-Cr. 21.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>22</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>278,899
-Cr. 27.89</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>278,899</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>27.89 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>58,969
-Cr. 5.90</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>278,877</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>27.89 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1262939</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>248,933
-Cr. 24.89</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-278,846</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-27.88 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>526225</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>519,754
-Cr. 51.98</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>519,754</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>51.98 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1966,48 +4210,150 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>16,048
-Cr. 1.60</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>6,687
-Cr. 0.67</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>11,132
-Cr. 1.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>11,132</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>4,445
-Cr. 0.44</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>11,131</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1335840</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>4,916
-Cr. 0.49</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-11,130</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>556600</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>20,171
-Cr. 2.02</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>20,171</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.02 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2019,48 +4365,150 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>308,081
-Cr. 30.81</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>31</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>128,367
-Cr. 12.84</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>13</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>217,100
-Cr. 21.71</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>217,100</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>21.71 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>88,733
-Cr. 8.87</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>217,087</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>21.71 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>1680774</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>90,981
-Cr. 9.10</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-217,069</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.71 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>700323</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>523,752
-Cr. 52.38</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>523,752</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.38 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2072,48 +4520,150 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>379,418
-Cr. 37.94</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>38</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>158,091
-Cr. 15.81</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>16</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>375,011
-Cr. 37.50</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>375,011</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.50 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>216,920
-Cr. 21.69</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>374,995</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.50 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>2368491</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>4,407
-Cr. 0.44</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-374,973</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-37.50 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>986871</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>374,596
-Cr. 37.46</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>374,596</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.46 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2125,48 +4675,150 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>14,563,547
-Cr. 1456.35</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,459</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.15 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>6,068,145
-Cr. 606.81</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>608</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.06 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7,021,141
-Cr. 702.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>7,021,141</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>702.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>952,996
-Cr. 95.30</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>7,020,533</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>702.05 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>1154951</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>7,542,406
-Cr. 754.24</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-7,019,682</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-701.97 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>481230</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>16,016,890
-Cr. 1601.69</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>16,016,890</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1601.69 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2187,11 +4839,11 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
@@ -2199,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-22T17:27:48+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2306,48 +4958,150 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1,068,752
-Cr. 106.88</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>107</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>445,313
-Cr. 44.53</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>45</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>860,139
-Cr. 86.01</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>860,139</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>86.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>414,826
-Cr. 41.48</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>860,094</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>86.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>1929284</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>208,613
-Cr. 20.86</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-860,032</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-86.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>803868</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>1,291,487
-Cr. 129.15</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,291,487</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>129.15 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2359,48 +5113,150 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>149,947
-Cr. 14.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>15</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>62,478
-Cr. 6.25</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>6</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>70,608
-Cr. 7.06</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>70,608</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.06 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>8,130
-Cr. 0.81</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>70,602</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.06 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>1129728</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>79,339
-Cr. 7.93</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-70,593</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-7.06 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>470720</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>164,506
-Cr. 16.45</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>164,506</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>16.45 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2412,48 +5268,150 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>3,878,724
-Cr. 387.87</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>388</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.04 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1,616,135
-Cr. 161.61</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>162</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.02 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1,916,509
-Cr. 191.65</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,916,509</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>191.65 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>300,374
-Cr. 30.04</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,916,347</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>191.63 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1185469</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1,962,215
-Cr. 196.22</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-1,916,121</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-191.61 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>493946</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>4,115,874
-Cr. 411.59</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>4,115,874</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>411.59 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2465,48 +5423,150 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>3,254,310
-Cr. 325.43</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>325</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.03 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>1,355,962
-Cr. 135.60</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>135</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1,824,117
-Cr. 182.41</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,824,117</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>182.41 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>468,154
-Cr. 46.82</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,823,982</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>182.40 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>1347040</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1,430,193
-Cr. 143.02</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-1,823,792</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-182.38 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>561267</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>3,623,756
-Cr. 362.38</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,623,756</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>362.38 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2518,48 +5578,150 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>4,703,356
-Cr. 470.34</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>470</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.05 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1,959,732
-Cr. 195.97</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>196</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.02 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2,715,415
-Cr. 271.54</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,715,415</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>271.54 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>755,683
-Cr. 75.57</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,715,219</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>271.52 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>1386595</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1,987,941
-Cr. 198.79</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-2,714,945</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-271.49 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>577748</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>5,106,358
-Cr. 510.64</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,106,358</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>510.64 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2571,48 +5733,150 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>13,055,089
-Cr. 1305.51</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,305</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.13 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5,439,620
-Cr. 543.96</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>544</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.05 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>7,386,788
-Cr. 738.68</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>7,386,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>738.68 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,947,168
-Cr. 194.72</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>7,386,244</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>738.62 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>1358490</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>5,668,301
-Cr. 566.83</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-7,385,483</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-738.55 Cr</t>
+          </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>566037</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>14,301,981
-Cr. 1430.20</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>14,301,981</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1430.20 Cr</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2727,20 +5991,71 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>160,903
-Cr. 16.09</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>160,903</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>16.09 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,992
-Cr. 7.80</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>77,992</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.80 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-82,911
-Cr. -8.29</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-82,911</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-8.29 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2767,20 +6082,71 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>32,227
-Cr. 3.22</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>32,227</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.22 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>11,801
-Cr. 1.18</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>11,801</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.18 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-20,426
-Cr. -2.04</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-20,426</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-2.04 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2807,20 +6173,71 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>120,318
-Cr. 12.03</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>120,318</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.03 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57,289
-Cr. 5.73</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>57,289</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.73 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-63,029
-Cr. -6.30</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-63,029</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-6.30 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -2847,20 +6264,71 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>507,420
-Cr. 50.74</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>507,420</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>50.74 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>363,937
-Cr. 36.39</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>363,937</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.39 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-143,483
-Cr. -14.35</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-143,483</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-14.35 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2887,20 +6355,71 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2,962,795
-Cr. 296.28</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,962,795</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>296.28 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,692,699
-Cr. 369.27</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,692,699</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>369.27 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>729,904
-Cr. 72.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>729,904</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>72.99 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2927,20 +6446,71 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>132,267
-Cr. 13.23</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>132,267</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.23 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>151,197
-Cr. 15.12</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>151,197</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.12 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>18,930
-Cr. 1.89</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>18,930</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.89 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2967,20 +6537,71 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>522,843
-Cr. 52.28</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>522,843</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.28 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>123,038
-Cr. 12.30</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>123,038</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.30 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-399,805
-Cr. -39.98</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-399,805</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-39.98 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3007,20 +6628,71 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>307,843
-Cr. 30.78</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>307,843</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.78 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>94,924
-Cr. 9.49</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>94,924</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.49 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-212,919
-Cr. -21.29</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-212,919</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.29 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3047,20 +6719,71 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3087,20 +6810,71 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>13,194
-Cr. 1.32</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>13,194</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.32 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>24,273
-Cr. 2.43</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>24,273</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.43 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>11,079
-Cr. 1.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>11,079</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3127,20 +6901,71 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>53,702
-Cr. 5.37</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>53,702</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.37 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5,129
-Cr. 0.51</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,129</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.51 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-48,573
-Cr. -4.86</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-48,573</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.86 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3167,20 +6992,71 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>97,500
-Cr. 9.75</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>97,500</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.75 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>59,852
-Cr. 5.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>59,852</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.99 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-37,648
-Cr. -3.76</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-37,648</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-3.76 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3207,20 +7083,71 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>310,912
-Cr. 31.09</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>310,912</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.09 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>131,048
-Cr. 13.10</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>131,048</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.10 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-179,864
-Cr. -17.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-179,864</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-17.99 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -3247,20 +7174,71 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3287,20 +7265,71 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>315,733
-Cr. 31.57</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>315,733</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.57 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>103,375
-Cr. 10.34</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>103,375</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.34 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-212,358
-Cr. -21.24</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-212,358</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.24 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3323,20 +7352,71 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>64,034
-Cr. 6.40</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>64,034</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.40 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>-64,034
-Cr. -6.40</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-64,034</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-6.40 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3363,20 +7443,71 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>6,010
-Cr. 0.60</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>6,010</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.60 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>-6,010
-Cr. -0.60</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-6,010</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.60 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3399,20 +7530,71 @@
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>5,607,701
-Cr. 560.77</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,607,701</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>560.77 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,896,554
-Cr. 489.66</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>4,896,554</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>489.66 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-711,147
-Cr. -71.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-711,147</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-71.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3532,20 +7714,71 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1,018,353
-Cr. 101.84</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,018,353</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>101.84 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>408,842
-Cr. 40.88</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>408,842</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>40.88 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>609,511
-Cr. 60.95</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>609,511</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>60.95 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3572,20 +7805,71 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>40,232
-Cr. 4.02</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>40,232</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.02 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>15,491
-Cr. 1.55</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>15,491</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.55 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>24,741
-Cr. 2.47</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>24,741</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.47 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3612,20 +7896,71 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>130,592
-Cr. 13.06</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>130,592</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.06 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>18,459
-Cr. 1.85</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>18,459</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.85 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>112,133
-Cr. 11.21</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>112,133</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.21 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3652,20 +7987,71 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -3692,20 +8078,71 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3,117,515
-Cr. 311.75</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,117,515</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>311.75 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,746,106
-Cr. 374.61</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,746,106</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>374.61 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-628,591
-Cr. -62.86</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-628,591</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-62.86 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3732,20 +8169,71 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3772,20 +8260,71 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>1,301,009
-Cr. 130.10</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,301,009</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>130.10 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>707,656
-Cr. 70.77</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>707,656</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>70.77 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>593,353
-Cr. 59.34</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>593,353</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>59.34 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-22T17:27:48+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2696,11 +2696,11 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
@@ -2708,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-22T17:27:48+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2820,19 +2820,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>671</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.07 Cr</t>
+            <t>6,706,409</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>670.64 Cr</t>
           </r>
         </is>
       </c>
@@ -2843,19 +2843,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>280</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.03 Cr</t>
+            <t>2,794,337</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>279.43 Cr</t>
           </r>
         </is>
       </c>
@@ -2889,25 +2889,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,071,543</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>307.15 Cr</t>
+            <t>277,486</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>27.75 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>1098715</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2917,25 +2917,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-3,071,152</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-307.12 Cr</t>
+            <t>3,634,586</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>363.46 Cr</t>
           </r>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>457798</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -2975,19 +2975,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>410</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.04 Cr</t>
+            <t>4,100,453</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>410.05 Cr</t>
           </r>
         </is>
       </c>
@@ -2998,19 +2998,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>171</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.02 Cr</t>
+            <t>1,708,522</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>170.85 Cr</t>
           </r>
         </is>
       </c>
@@ -3044,25 +3044,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,966,447</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>196.64 Cr</t>
+            <t>258,096</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>25.81 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1151191</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3072,25 +3072,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,966,208</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-196.62 Cr</t>
+            <t>2,133,835</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>213.38 Cr</t>
           </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>479663</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -3130,19 +3130,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>29</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>285,089</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.51 Cr</t>
           </r>
         </is>
       </c>
@@ -3153,19 +3153,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>12</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>118,787</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.88 Cr</t>
           </r>
         </is>
       </c>
@@ -3199,25 +3199,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>60</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.01 Cr</t>
+            <t>-118,715</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-11.87 Cr</t>
           </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -3227,25 +3227,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-43</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-0.00 Cr</t>
+            <t>285,017</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.50 Cr</t>
           </r>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3285,19 +3285,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>78</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.01 Cr</t>
+            <t>776,198</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>77.62 Cr</t>
           </r>
         </is>
       </c>
@@ -3308,19 +3308,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>323,416</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.34 Cr</t>
           </r>
         </is>
       </c>
@@ -3354,25 +3354,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>337,330</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.73 Cr</t>
+            <t>13,946</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.39 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1038037</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3382,25 +3382,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-337,284</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-33.73 Cr</t>
+            <t>438,836</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>43.88 Cr</t>
           </r>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>432515</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -3440,19 +3440,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>50</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.01 Cr</t>
+            <t>496,609</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>49.66 Cr</t>
           </r>
         </is>
       </c>
@@ -3463,19 +3463,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>21</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>206,920</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>20.69 Cr</t>
           </r>
         </is>
       </c>
@@ -3509,25 +3509,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>216,376</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.64 Cr</t>
+            <t>9,477</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.95 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1038706</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3537,25 +3537,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-216,347</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-21.63 Cr</t>
+            <t>280,212</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.02 Cr</t>
           </r>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>432794</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3595,19 +3595,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>68</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.01 Cr</t>
+            <t>680,197</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>68.02 Cr</t>
           </r>
         </is>
       </c>
@@ -3618,19 +3618,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>28</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>283,415</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.34 Cr</t>
           </r>
         </is>
       </c>
@@ -3664,25 +3664,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>364,625</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.46 Cr</t>
+            <t>81,238</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.12 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1287011</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -3692,25 +3692,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-364,585</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-36.46 Cr</t>
+            <t>315,544</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.55 Cr</t>
           </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>536254</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -3750,19 +3750,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>8</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>77,300</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.73 Cr</t>
           </r>
         </is>
       </c>
@@ -3773,19 +3773,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>32,208</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.22 Cr</t>
           </r>
         </is>
       </c>
@@ -3819,25 +3819,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>59,579</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.96 Cr</t>
+            <t>27,374</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.74 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>1787460</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3847,25 +3847,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-59,574</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-5.96 Cr</t>
+            <t>17,718</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.77 Cr</t>
           </r>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>744775</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3905,19 +3905,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>21</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>209,913</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>20.99 Cr</t>
           </r>
         </is>
       </c>
@@ -3928,19 +3928,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>9</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>87,464</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.75 Cr</t>
           </r>
         </is>
       </c>
@@ -3974,25 +3974,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>122,483</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>12.25 Cr</t>
+            <t>35,028</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.50 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>1399909</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -4002,25 +4002,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-122,471</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-12.25 Cr</t>
+            <t>87,421</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.74 Cr</t>
           </r>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>583295</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -4060,19 +4060,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>53</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.01 Cr</t>
+            <t>527,832</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.78 Cr</t>
           </r>
         </is>
       </c>
@@ -4083,19 +4083,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>22</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>219,930</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>21.99 Cr</t>
           </r>
         </is>
       </c>
@@ -4129,25 +4129,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>278,877</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>27.89 Cr</t>
+            <t>58,969</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.90 Cr</t>
           </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>1262939</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -4157,25 +4157,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-278,846</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-27.88 Cr</t>
+            <t>248,933</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>24.89 Cr</t>
           </r>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>526225</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4215,19 +4215,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>16,048</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.60 Cr</t>
           </r>
         </is>
       </c>
@@ -4238,19 +4238,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>6,687</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.67 Cr</t>
           </r>
         </is>
       </c>
@@ -4284,25 +4284,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,131</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.11 Cr</t>
+            <t>4,445</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.44 Cr</t>
           </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1335840</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4312,25 +4312,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-11,130</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-1.11 Cr</t>
+            <t>4,916</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.49 Cr</t>
           </r>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>556600</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -4370,19 +4370,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>31</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>308,081</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.81 Cr</t>
           </r>
         </is>
       </c>
@@ -4393,19 +4393,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>13</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>128,367</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.84 Cr</t>
           </r>
         </is>
       </c>
@@ -4439,25 +4439,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>217,087</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.71 Cr</t>
+            <t>88,733</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.87 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>1680774</t>
+          <t>169</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4467,25 +4467,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-217,069</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-21.71 Cr</t>
+            <t>90,981</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.10 Cr</t>
           </r>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>700323</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4525,19 +4525,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>38</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>379,418</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.94 Cr</t>
           </r>
         </is>
       </c>
@@ -4548,19 +4548,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>158,091</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.81 Cr</t>
           </r>
         </is>
       </c>
@@ -4594,25 +4594,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>374,995</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.50 Cr</t>
+            <t>216,920</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>21.69 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2368491</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -4622,25 +4622,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-374,973</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-37.50 Cr</t>
+            <t>4,407</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.44 Cr</t>
           </r>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>986871</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -4680,19 +4680,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,459</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.15 Cr</t>
+            <t>14,563,547</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1456.35 Cr</t>
           </r>
         </is>
       </c>
@@ -4703,19 +4703,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>608</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.06 Cr</t>
+            <t>6,068,145</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>606.81 Cr</t>
           </r>
         </is>
       </c>
@@ -4749,25 +4749,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>7,020,533</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>702.05 Cr</t>
+            <t>952,996</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>95.30 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1154951</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4777,25 +4777,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-7,019,682</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-701.97 Cr</t>
+            <t>7,542,406</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>754.24 Cr</t>
           </r>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>481230</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4839,11 +4839,11 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
@@ -4851,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-22T17:27:48+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4963,19 +4963,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>107</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.01 Cr</t>
+            <t>1,068,752</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>106.88 Cr</t>
           </r>
         </is>
       </c>
@@ -4986,19 +4986,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>45</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>445,313</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>44.53 Cr</t>
           </r>
         </is>
       </c>
@@ -5032,25 +5032,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>860,094</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.01 Cr</t>
+            <t>414,826</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>41.48 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>1929284</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -5060,25 +5060,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-860,032</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-86.00 Cr</t>
+            <t>208,613</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>20.86 Cr</t>
           </r>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>803868</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -5118,19 +5118,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>15</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>149,947</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.99 Cr</t>
           </r>
         </is>
       </c>
@@ -5141,19 +5141,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.00 Cr</t>
+            <t>62,478</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.25 Cr</t>
           </r>
         </is>
       </c>
@@ -5187,25 +5187,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>70,602</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.06 Cr</t>
+            <t>8,130</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.81 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1129728</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5215,25 +5215,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-70,593</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-7.06 Cr</t>
+            <t>79,339</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.93 Cr</t>
           </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>470720</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5273,19 +5273,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>388</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.04 Cr</t>
+            <t>3,878,724</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>387.87 Cr</t>
           </r>
         </is>
       </c>
@@ -5296,19 +5296,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>162</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.02 Cr</t>
+            <t>1,616,135</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>161.61 Cr</t>
           </r>
         </is>
       </c>
@@ -5342,25 +5342,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,916,347</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>191.63 Cr</t>
+            <t>300,374</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.04 Cr</t>
           </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>1185469</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -5370,25 +5370,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,916,121</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-191.61 Cr</t>
+            <t>1,962,215</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>196.22 Cr</t>
           </r>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>493946</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5428,19 +5428,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>325</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.03 Cr</t>
+            <t>3,254,310</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>325.43 Cr</t>
           </r>
         </is>
       </c>
@@ -5451,19 +5451,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>135</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.01 Cr</t>
+            <t>1,355,962</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>135.60 Cr</t>
           </r>
         </is>
       </c>
@@ -5497,25 +5497,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,823,982</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>182.40 Cr</t>
+            <t>468,154</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>46.82 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1347040</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -5525,25 +5525,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,823,792</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-182.38 Cr</t>
+            <t>1,430,193</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>143.02 Cr</t>
           </r>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>561267</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -5583,19 +5583,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>470</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.05 Cr</t>
+            <t>4,703,356</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>470.34 Cr</t>
           </r>
         </is>
       </c>
@@ -5606,19 +5606,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>196</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.02 Cr</t>
+            <t>1,959,732</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>195.97 Cr</t>
           </r>
         </is>
       </c>
@@ -5652,25 +5652,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,715,219</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>271.52 Cr</t>
+            <t>755,683</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>75.57 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1386595</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -5680,25 +5680,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-2,714,945</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-271.49 Cr</t>
+            <t>1,987,941</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>198.79 Cr</t>
           </r>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>577748</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5738,19 +5738,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,305</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.13 Cr</t>
+            <t>13,055,089</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1305.51 Cr</t>
           </r>
         </is>
       </c>
@@ -5761,19 +5761,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>544</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.05 Cr</t>
+            <t>5,439,620</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>543.96 Cr</t>
           </r>
         </is>
       </c>
@@ -5807,25 +5807,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>7,386,244</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>738.62 Cr</t>
+            <t>1,947,168</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>194.72 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1358490</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5835,25 +5835,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-7,385,483</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-738.55 Cr</t>
+            <t>5,668,301</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>566.83 Cr</t>
           </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>566037</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -5907,7 +5907,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 05.09.2026</t>
+          <t>Open Line FR Report - As On 25.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6019,19 +6019,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>77,992</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.80 Cr</t>
+            <t>81,555</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.16 Cr</t>
           </r>
         </is>
       </c>
@@ -6042,25 +6042,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-82,911</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-8.29 Cr</t>
+            <t>-79,348</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-7.93 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -6110,19 +6110,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,801</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.18 Cr</t>
+            <t>12,767</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.28 Cr</t>
           </r>
         </is>
       </c>
@@ -6133,25 +6133,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-20,426</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-2.04 Cr</t>
+            <t>-19,460</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.95 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>39.62</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -6201,19 +6201,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>57,289</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.73 Cr</t>
+            <t>64,676</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.47 Cr</t>
           </r>
         </is>
       </c>
@@ -6224,25 +6224,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-63,029</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-6.30 Cr</t>
+            <t>-55,642</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-5.56 Cr</t>
           </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -6292,19 +6292,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>363,937</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.39 Cr</t>
+            <t>379,202</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.92 Cr</t>
           </r>
         </is>
       </c>
@@ -6315,25 +6315,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-143,483</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-14.35 Cr</t>
+            <t>-128,218</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-12.82 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -6383,19 +6383,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,692,699</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>369.27 Cr</t>
+            <t>3,805,865</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>380.59 Cr</t>
           </r>
         </is>
       </c>
@@ -6406,25 +6406,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>729,904</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>72.99 Cr</t>
+            <t>843,070</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>84.31 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>124.64</t>
+          <t>128.46</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -6474,19 +6474,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>151,197</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>15.12 Cr</t>
+            <t>183,938</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.39 Cr</t>
           </r>
         </is>
       </c>
@@ -6497,25 +6497,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,930</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.89 Cr</t>
+            <t>51,671</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>114.31</t>
+          <t>139.07</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -6565,19 +6565,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>123,038</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>12.30 Cr</t>
+            <t>140,407</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.04 Cr</t>
           </r>
         </is>
       </c>
@@ -6588,25 +6588,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-399,805</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-39.98 Cr</t>
+            <t>-382,436</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-38.24 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -6656,19 +6656,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>94,924</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>9.49 Cr</t>
+            <t>105,095</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.51 Cr</t>
           </r>
         </is>
       </c>
@@ -6679,25 +6679,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-212,919</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-21.29 Cr</t>
+            <t>-202,748</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.27 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>34.14</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -6815,19 +6815,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>13,194</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.32 Cr</t>
+            <t>40,372</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.04 Cr</t>
           </r>
         </is>
       </c>
@@ -6838,19 +6838,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>24,273</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.43 Cr</t>
+            <t>25,991</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.60 Cr</t>
           </r>
         </is>
       </c>
@@ -6861,25 +6861,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,079</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.11 Cr</t>
+            <t>-14,381</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.44 Cr</t>
           </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>183.97</t>
+          <t>64.38</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -6929,19 +6929,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,129</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.51 Cr</t>
+            <t>5,681</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.57 Cr</t>
           </r>
         </is>
       </c>
@@ -6952,25 +6952,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-48,573</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.86 Cr</t>
+            <t>-48,021</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.80 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -7020,19 +7020,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>59,852</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.99 Cr</t>
+            <t>71,111</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.11 Cr</t>
           </r>
         </is>
       </c>
@@ -7043,25 +7043,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-37,648</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-3.76 Cr</t>
+            <t>-26,389</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-2.64 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>72.93</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -7111,19 +7111,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>131,048</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.10 Cr</t>
+            <t>147,126</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.71 Cr</t>
           </r>
         </is>
       </c>
@@ -7134,25 +7134,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-179,864</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-17.99 Cr</t>
+            <t>-163,786</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-16.38 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -7293,19 +7293,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>103,375</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>10.34 Cr</t>
+            <t>112,585</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.26 Cr</t>
           </r>
         </is>
       </c>
@@ -7316,25 +7316,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-212,358</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-21.24 Cr</t>
+            <t>-203,148</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.31 Cr</t>
           </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -7535,19 +7535,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,607,701</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>560.77 Cr</t>
+            <t>5,634,879</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>563.49 Cr</t>
           </r>
         </is>
       </c>
@@ -7558,19 +7558,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,896,554</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>489.66 Cr</t>
+            <t>5,135,999</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>513.60 Cr</t>
           </r>
         </is>
       </c>
@@ -7581,25 +7581,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-711,147</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-71.11 Cr</t>
+            <t>-498,880</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-49.89 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>91.15</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -7635,7 +7635,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 25.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -7719,19 +7719,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,018,353</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>101.84 Cr</t>
+            <t>1,045,531</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>104.55 Cr</t>
           </r>
         </is>
       </c>
@@ -7742,19 +7742,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>408,842</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>40.88 Cr</t>
+            <t>457,028</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>45.70 Cr</t>
           </r>
         </is>
       </c>
@@ -7765,30 +7765,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>609,511</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>60.95 Cr</t>
+            <t>588,503</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>58.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>56.29</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -7833,19 +7833,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>15,491</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.55 Cr</t>
+            <t>21,238</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.12 Cr</t>
           </r>
         </is>
       </c>
@@ -7856,30 +7856,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>24,741</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.47 Cr</t>
+            <t>18,994</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.90 Cr</t>
           </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>52.79</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -8106,19 +8106,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,746,106</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>374.61 Cr</t>
+            <t>3,844,908</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>384.49 Cr</t>
           </r>
         </is>
       </c>
@@ -8129,30 +8129,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-628,591</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-62.86 Cr</t>
+            <t>-727,393</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-72.74 Cr</t>
           </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>123.33</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-23.33</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -8288,19 +8288,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>707,656</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>70.77 Cr</t>
+            <t>794,366</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>79.44 Cr</t>
           </r>
         </is>
       </c>
@@ -8311,30 +8311,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>593,353</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>59.34 Cr</t>
+            <t>506,643</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>50.66 Cr</t>
           </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>61.06</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Open Line FR Report - As On 25." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Open Line FR Report - As On 25." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2708,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4851,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - SEP 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - SEP 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - SE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -557,14 +557,14 @@
         <is>
           <t>B
 BP
-A / 12 * 5</t>
+A / 12 * 6</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals up to AUG 2026</t>
+Actuals up to SEP 2026</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -644,19 +644,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>267,301</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>26.73 Cr</t>
+            <t>320,761</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.08 Cr</t>
           </r>
         </is>
       </c>
@@ -667,19 +667,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>294,135</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>29.41 Cr</t>
+            <t>350,760</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.08 Cr</t>
           </r>
         </is>
       </c>
@@ -690,25 +690,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>26,834</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.68 Cr</t>
+            <t>29,999</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -718,25 +718,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>347,387</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>34.74 Cr</t>
+            <t>290,762</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>29.08 Cr</t>
           </r>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -804,19 +804,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,503,709</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>150.37 Cr</t>
+            <t>1,804,451</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>180.45 Cr</t>
           </r>
         </is>
       </c>
@@ -827,19 +827,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,781,320</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>178.13 Cr</t>
+            <t>2,122,627</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>212.26 Cr</t>
           </r>
         </is>
       </c>
@@ -850,19 +850,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>277,611</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>27.76 Cr</t>
+            <t>318,176</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.82 Cr</t>
           </r>
         </is>
       </c>
@@ -878,25 +878,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,827,582</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>182.76 Cr</t>
+            <t>1,486,275</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>148.63 Cr</t>
           </r>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -964,19 +964,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>777,018</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>77.70 Cr</t>
+            <t>932,422</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>93.24 Cr</t>
           </r>
         </is>
       </c>
@@ -1010,25 +1010,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,014</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.50 Cr</t>
+            <t>-150,390</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-15.04 Cr</t>
           </r>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1124,19 +1124,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>563,992</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>56.40 Cr</t>
+            <t>676,790</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>67.68 Cr</t>
           </r>
         </is>
       </c>
@@ -1147,19 +1147,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>911,131</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>91.11 Cr</t>
+            <t>1,015,079</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>101.51 Cr</t>
           </r>
         </is>
       </c>
@@ -1170,25 +1170,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>347,139</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>34.71 Cr</t>
+            <t>338,288</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.83 Cr</t>
           </r>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1198,25 +1198,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>442,450</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>44.24 Cr</t>
+            <t>338,502</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1284,19 +1284,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>858,312</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>85.83 Cr</t>
+            <t>1,029,975</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>103.00 Cr</t>
           </r>
         </is>
       </c>
@@ -1307,19 +1307,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>995,022</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>99.50 Cr</t>
+            <t>1,163,224</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>116.32 Cr</t>
           </r>
         </is>
       </c>
@@ -1330,25 +1330,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>136,710</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.67 Cr</t>
+            <t>133,249</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.32 Cr</t>
           </r>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1358,25 +1358,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,064,928</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>106.49 Cr</t>
+            <t>896,726</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>89.67 Cr</t>
           </r>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1444,19 +1444,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,396,902</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>139.69 Cr</t>
+            <t>1,676,283</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>167.63 Cr</t>
           </r>
         </is>
       </c>
@@ -1467,19 +1467,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,978,638</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>197.86 Cr</t>
+            <t>2,316,412</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>231.64 Cr</t>
           </r>
         </is>
       </c>
@@ -1490,25 +1490,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>581,736</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>58.17 Cr</t>
+            <t>640,129</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>64.01 Cr</t>
           </r>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1518,25 +1518,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,373,928</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>137.39 Cr</t>
+            <t>1,036,154</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>103.62 Cr</t>
           </r>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1604,19 +1604,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,845,319</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>184.53 Cr</t>
+            <t>2,214,383</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>221.44 Cr</t>
           </r>
         </is>
       </c>
@@ -1627,19 +1627,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,192,865</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>219.29 Cr</t>
+            <t>2,600,978</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>260.10 Cr</t>
           </r>
         </is>
       </c>
@@ -1650,25 +1650,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>347,546</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>34.75 Cr</t>
+            <t>386,595</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.66 Cr</t>
           </r>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1678,25 +1678,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,235,901</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>223.59 Cr</t>
+            <t>1,827,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>182.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1764,19 +1764,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,836,336</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>483.63 Cr</t>
+            <t>5,803,603</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>580.36 Cr</t>
           </r>
         </is>
       </c>
@@ -1787,19 +1787,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,702,475</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>570.25 Cr</t>
+            <t>5,756,378</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>575.64 Cr</t>
           </r>
         </is>
       </c>
@@ -1810,25 +1810,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>866,139</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.61 Cr</t>
+            <t>-47,225</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.72 Cr</t>
           </r>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1838,25 +1838,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,904,731</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>590.47 Cr</t>
+            <t>5,850,828</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>585.08 Cr</t>
           </r>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1924,19 +1924,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>580,347</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>58.03 Cr</t>
+            <t>696,416</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>69.64 Cr</t>
           </r>
         </is>
       </c>
@@ -1947,19 +1947,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>916,954</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>91.70 Cr</t>
+            <t>1,052,451</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.25 Cr</t>
           </r>
         </is>
       </c>
@@ -1970,25 +1970,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>336,607</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.66 Cr</t>
+            <t>356,035</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.60 Cr</t>
           </r>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1998,25 +1998,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>475,878</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>47.59 Cr</t>
+            <t>340,381</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>34.04 Cr</t>
           </r>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2084,19 +2084,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>414,432</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>41.44 Cr</t>
+            <t>497,319</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>49.73 Cr</t>
           </r>
         </is>
       </c>
@@ -2107,19 +2107,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>441,761</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>44.18 Cr</t>
+            <t>528,378</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.84 Cr</t>
           </r>
         </is>
       </c>
@@ -2130,25 +2130,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>27,328</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.73 Cr</t>
+            <t>31,059</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.11 Cr</t>
           </r>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -2158,25 +2158,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>552,877</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>55.29 Cr</t>
+            <t>466,260</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>46.63 Cr</t>
           </r>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -2244,19 +2244,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>537,945</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>53.79 Cr</t>
+            <t>645,534</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>64.55 Cr</t>
           </r>
         </is>
       </c>
@@ -2267,19 +2267,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>532,662</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>53.27 Cr</t>
+            <t>639,713</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>63.97 Cr</t>
           </r>
         </is>
       </c>
@@ -2290,19 +2290,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-5,283</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-0.53 Cr</t>
+            <t>-5,820</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.58 Cr</t>
           </r>
         </is>
       </c>
@@ -2318,25 +2318,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>758,405</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>75.84 Cr</t>
+            <t>651,354</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>65.14 Cr</t>
           </r>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2400,19 +2400,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>13,581,614</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1358.16 Cr</t>
+            <t>16,297,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1629.79 Cr</t>
           </r>
         </is>
       </c>
@@ -2423,19 +2423,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,528,995</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1652.90 Cr</t>
+            <t>18,328,032</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1832.80 Cr</t>
           </r>
         </is>
       </c>
@@ -2446,25 +2446,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,947,381</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>294.74 Cr</t>
+            <t>2,030,096</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>203.01 Cr</t>
           </r>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2474,25 +2474,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,066,878</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1606.69 Cr</t>
+            <t>14,267,841</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1426.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -2560,19 +2560,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-5,435</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-0.54 Cr</t>
+            <t>-6,522</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.65 Cr</t>
           </r>
         </is>
       </c>
@@ -2583,19 +2583,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,578,052</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>157.81 Cr</t>
+            <t>1,591,631</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.16 Cr</t>
           </r>
         </is>
       </c>
@@ -2606,25 +2606,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,583,487</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>158.35 Cr</t>
+            <t>1,598,154</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.82 Cr</t>
           </r>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-29033</t>
+          <t>-24402</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2634,25 +2634,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,591,097</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-159.11 Cr</t>
+            <t>-1,604,676</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-160.47 Cr</t>
           </r>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12097</t>
+          <t>-12201</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -2708,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
+          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2761,14 +2761,14 @@
         <is>
           <t>B
 BP
-A / 12 * 5</t>
+A / 12 * 6</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals up to AUG 2026</t>
+Actuals up to SEP 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2843,19 +2843,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,794,337</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>279.43 Cr</t>
+            <t>3,353,204</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>335.32 Cr</t>
           </r>
         </is>
       </c>
@@ -2866,19 +2866,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,071,823</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>307.18 Cr</t>
+            <t>3,689,447</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>368.94 Cr</t>
           </r>
         </is>
       </c>
@@ -2889,19 +2889,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>277,486</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>27.75 Cr</t>
+            <t>336,242</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.62 Cr</t>
           </r>
         </is>
       </c>
@@ -2917,25 +2917,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,634,586</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>363.46 Cr</t>
+            <t>3,016,962</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>301.70 Cr</t>
           </r>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -2998,19 +2998,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,708,522</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>170.85 Cr</t>
+            <t>2,050,226</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>205.02 Cr</t>
           </r>
         </is>
       </c>
@@ -3021,19 +3021,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,966,618</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>196.66 Cr</t>
+            <t>2,354,387</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>235.44 Cr</t>
           </r>
         </is>
       </c>
@@ -3044,19 +3044,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>258,096</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>25.81 Cr</t>
+            <t>304,160</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.42 Cr</t>
           </r>
         </is>
       </c>
@@ -3072,25 +3072,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,133,835</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>213.38 Cr</t>
+            <t>1,746,066</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>174.61 Cr</t>
           </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -3153,19 +3153,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>118,787</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.88 Cr</t>
+            <t>142,544</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.25 Cr</t>
           </r>
         </is>
       </c>
@@ -3199,19 +3199,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-118,715</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-11.87 Cr</t>
+            <t>-142,472</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-14.25 Cr</t>
           </r>
         </is>
       </c>
@@ -3308,19 +3308,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>323,416</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.34 Cr</t>
+            <t>388,099</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.81 Cr</t>
           </r>
         </is>
       </c>
@@ -3331,19 +3331,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>337,362</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.74 Cr</t>
+            <t>405,401</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>40.54 Cr</t>
           </r>
         </is>
       </c>
@@ -3354,19 +3354,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>13,946</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.39 Cr</t>
+            <t>17,302</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.73 Cr</t>
           </r>
         </is>
       </c>
@@ -3382,25 +3382,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>438,836</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>43.88 Cr</t>
+            <t>370,797</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.08 Cr</t>
           </r>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -3463,19 +3463,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>206,920</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>20.69 Cr</t>
+            <t>248,304</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>24.83 Cr</t>
           </r>
         </is>
       </c>
@@ -3486,19 +3486,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>216,397</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.64 Cr</t>
+            <t>259,448</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>25.94 Cr</t>
           </r>
         </is>
       </c>
@@ -3509,25 +3509,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>9,477</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.95 Cr</t>
+            <t>11,144</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.11 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3537,25 +3537,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>280,212</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>28.02 Cr</t>
+            <t>237,161</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>23.72 Cr</t>
           </r>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3618,19 +3618,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>283,415</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>28.34 Cr</t>
+            <t>340,098</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>34.01 Cr</t>
           </r>
         </is>
       </c>
@@ -3641,19 +3641,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>364,653</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.47 Cr</t>
+            <t>437,059</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>43.71 Cr</t>
           </r>
         </is>
       </c>
@@ -3664,19 +3664,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>81,238</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.12 Cr</t>
+            <t>96,960</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.70 Cr</t>
           </r>
         </is>
       </c>
@@ -3692,25 +3692,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>315,544</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>31.55 Cr</t>
+            <t>243,138</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>24.31 Cr</t>
           </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -3773,19 +3773,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,208</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.22 Cr</t>
+            <t>38,650</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.87 Cr</t>
           </r>
         </is>
       </c>
@@ -3796,19 +3796,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>59,582</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.96 Cr</t>
+            <t>59,779</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.98 Cr</t>
           </r>
         </is>
       </c>
@@ -3819,25 +3819,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>27,374</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.74 Cr</t>
+            <t>21,129</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.11 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>155</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3847,19 +3847,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>17,718</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.77 Cr</t>
+            <t>17,521</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.75 Cr</t>
           </r>
         </is>
       </c>
@@ -3928,19 +3928,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>87,464</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.75 Cr</t>
+            <t>104,956</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.50 Cr</t>
           </r>
         </is>
       </c>
@@ -3951,19 +3951,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>122,492</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>12.25 Cr</t>
+            <t>147,747</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.77 Cr</t>
           </r>
         </is>
       </c>
@@ -3974,25 +3974,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>35,028</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.50 Cr</t>
+            <t>42,790</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.28 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -4002,25 +4002,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>87,421</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.74 Cr</t>
+            <t>62,166</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.22 Cr</t>
           </r>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -4083,19 +4083,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>219,930</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.99 Cr</t>
+            <t>263,916</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>26.39 Cr</t>
           </r>
         </is>
       </c>
@@ -4106,19 +4106,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>278,899</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>27.89 Cr</t>
+            <t>318,467</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.85 Cr</t>
           </r>
         </is>
       </c>
@@ -4129,25 +4129,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>58,969</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.90 Cr</t>
+            <t>54,551</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.46 Cr</t>
           </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -4157,25 +4157,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>248,933</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>24.89 Cr</t>
+            <t>209,365</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>20.94 Cr</t>
           </r>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4238,19 +4238,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,687</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.67 Cr</t>
+            <t>8,024</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.80 Cr</t>
           </r>
         </is>
       </c>
@@ -4261,19 +4261,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,132</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.11 Cr</t>
+            <t>13,236</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.32 Cr</t>
           </r>
         </is>
       </c>
@@ -4284,25 +4284,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,445</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.44 Cr</t>
+            <t>5,212</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.52 Cr</t>
           </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4312,25 +4312,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,916</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.49 Cr</t>
+            <t>2,812</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.28 Cr</t>
           </r>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -4393,19 +4393,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>128,367</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>12.84 Cr</t>
+            <t>154,040</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.40 Cr</t>
           </r>
         </is>
       </c>
@@ -4416,19 +4416,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>217,100</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.71 Cr</t>
+            <t>265,202</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>26.52 Cr</t>
           </r>
         </is>
       </c>
@@ -4439,25 +4439,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>88,733</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.87 Cr</t>
+            <t>111,162</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.12 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4467,25 +4467,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>90,981</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>9.10 Cr</t>
+            <t>42,879</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.29 Cr</t>
           </r>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4548,19 +4548,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>158,091</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>15.81 Cr</t>
+            <t>189,709</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.97 Cr</t>
           </r>
         </is>
       </c>
@@ -4571,19 +4571,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>375,011</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.50 Cr</t>
+            <t>384,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.49 Cr</t>
           </r>
         </is>
       </c>
@@ -4594,25 +4594,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>216,920</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.69 Cr</t>
+            <t>195,227</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>19.52 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -4622,25 +4622,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,407</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.44 Cr</t>
+            <t>-5,518</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.55 Cr</t>
           </r>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -4703,19 +4703,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,068,145</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>606.81 Cr</t>
+            <t>7,281,774</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>728.18 Cr</t>
           </r>
         </is>
       </c>
@@ -4726,19 +4726,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>7,021,141</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>702.11 Cr</t>
+            <t>8,335,181</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>833.52 Cr</t>
           </r>
         </is>
       </c>
@@ -4749,25 +4749,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>952,996</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>95.30 Cr</t>
+            <t>1,053,408</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.34 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4777,25 +4777,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>7,542,406</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>754.24 Cr</t>
+            <t>6,228,366</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>622.84 Cr</t>
           </r>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4851,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4904,14 +4904,14 @@
         <is>
           <t>B
 BP
-A / 12 * 5</t>
+A / 12 * 6</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals up to AUG 2026</t>
+Actuals up to SEP 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4986,19 +4986,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>445,313</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>44.53 Cr</t>
+            <t>534,376</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>53.44 Cr</t>
           </r>
         </is>
       </c>
@@ -5009,19 +5009,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>860,139</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.01 Cr</t>
+            <t>862,766</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>86.28 Cr</t>
           </r>
         </is>
       </c>
@@ -5032,25 +5032,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>414,826</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>41.48 Cr</t>
+            <t>328,390</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.84 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>161</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -5060,25 +5060,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>208,613</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>20.86 Cr</t>
+            <t>205,986</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>20.60 Cr</t>
           </r>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -5141,19 +5141,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>62,478</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>6.25 Cr</t>
+            <t>74,974</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.50 Cr</t>
           </r>
         </is>
       </c>
@@ -5164,19 +5164,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>70,608</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.06 Cr</t>
+            <t>79,644</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.96 Cr</t>
           </r>
         </is>
       </c>
@@ -5187,25 +5187,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>8,130</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.81 Cr</t>
+            <t>4,670</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.47 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5215,25 +5215,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>79,339</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.93 Cr</t>
+            <t>70,303</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.03 Cr</t>
           </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5296,19 +5296,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,616,135</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>161.61 Cr</t>
+            <t>1,939,362</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>193.94 Cr</t>
           </r>
         </is>
       </c>
@@ -5319,19 +5319,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,916,509</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>191.65 Cr</t>
+            <t>2,011,062</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>201.11 Cr</t>
           </r>
         </is>
       </c>
@@ -5342,25 +5342,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>300,374</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>30.04 Cr</t>
+            <t>71,700</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -5370,25 +5370,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,962,215</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>196.22 Cr</t>
+            <t>1,867,662</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>186.77 Cr</t>
           </r>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5451,19 +5451,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,355,962</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>135.60 Cr</t>
+            <t>1,627,155</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>162.72 Cr</t>
           </r>
         </is>
       </c>
@@ -5474,19 +5474,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,824,117</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>182.41 Cr</t>
+            <t>2,013,588</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>201.36 Cr</t>
           </r>
         </is>
       </c>
@@ -5497,25 +5497,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>468,154</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>46.82 Cr</t>
+            <t>386,433</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.64 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -5525,25 +5525,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,430,193</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>143.02 Cr</t>
+            <t>1,240,722</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>124.07 Cr</t>
           </r>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -5606,19 +5606,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,959,732</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>195.97 Cr</t>
+            <t>2,351,678</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>235.17 Cr</t>
           </r>
         </is>
       </c>
@@ -5652,25 +5652,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>755,683</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>75.57 Cr</t>
+            <t>363,737</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.37 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -5761,19 +5761,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,439,620</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>543.96 Cr</t>
+            <t>6,527,544</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>652.75 Cr</t>
           </r>
         </is>
       </c>
@@ -5784,19 +5784,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>7,386,788</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>738.68 Cr</t>
+            <t>7,682,475</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>768.25 Cr</t>
           </r>
         </is>
       </c>
@@ -5807,25 +5807,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,947,168</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>194.72 Cr</t>
+            <t>1,154,930</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>115.49 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5835,25 +5835,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,668,301</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>566.83 Cr</t>
+            <t>5,372,614</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>537.26 Cr</t>
           </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - SEP 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - SEP 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - SE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -667,19 +667,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>350,760</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>35.08 Cr</t>
+            <t>353,512</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.35 Cr</t>
           </r>
         </is>
       </c>
@@ -690,25 +690,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>29,999</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.00 Cr</t>
+            <t>32,751</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.28 Cr</t>
           </r>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -718,19 +718,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>290,762</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>29.08 Cr</t>
+            <t>288,010</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.80 Cr</t>
           </r>
         </is>
       </c>
@@ -827,19 +827,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,122,627</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>212.26 Cr</t>
+            <t>2,126,374</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>212.64 Cr</t>
           </r>
         </is>
       </c>
@@ -850,19 +850,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>318,176</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>31.82 Cr</t>
+            <t>321,923</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.19 Cr</t>
           </r>
         </is>
       </c>
@@ -878,19 +878,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,486,275</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>148.63 Cr</t>
+            <t>1,482,528</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>148.25 Cr</t>
           </r>
         </is>
       </c>
@@ -1147,19 +1147,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,015,079</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>101.51 Cr</t>
+            <t>1,050,104</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.01 Cr</t>
           </r>
         </is>
       </c>
@@ -1170,25 +1170,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>338,288</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.83 Cr</t>
+            <t>373,314</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.33 Cr</t>
           </r>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1198,25 +1198,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>338,502</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.85 Cr</t>
+            <t>303,477</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.35 Cr</t>
           </r>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1307,19 +1307,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,163,224</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>116.32 Cr</t>
+            <t>1,192,410</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>119.24 Cr</t>
           </r>
         </is>
       </c>
@@ -1330,25 +1330,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>133,249</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.32 Cr</t>
+            <t>162,435</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>16.24 Cr</t>
           </r>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1358,25 +1358,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>896,726</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>89.67 Cr</t>
+            <t>867,540</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>86.75 Cr</t>
           </r>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1467,19 +1467,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,316,412</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>231.64 Cr</t>
+            <t>2,344,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>234.48 Cr</t>
           </r>
         </is>
       </c>
@@ -1490,25 +1490,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>640,129</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>64.01 Cr</t>
+            <t>668,505</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>66.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1518,25 +1518,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,036,154</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>103.62 Cr</t>
+            <t>1,007,778</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>100.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1627,19 +1627,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,600,978</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>260.10 Cr</t>
+            <t>2,602,601</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>260.26 Cr</t>
           </r>
         </is>
       </c>
@@ -1650,25 +1650,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>386,595</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.66 Cr</t>
+            <t>388,218</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.82 Cr</t>
           </r>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1678,19 +1678,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,827,788</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>182.78 Cr</t>
+            <t>1,826,165</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>182.62 Cr</t>
           </r>
         </is>
       </c>
@@ -1787,19 +1787,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,756,378</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>575.64 Cr</t>
+            <t>7,243,570</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>724.36 Cr</t>
           </r>
         </is>
       </c>
@@ -1810,25 +1810,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-47,225</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.72 Cr</t>
+            <t>1,439,967</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>144.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1838,25 +1838,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,850,828</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>585.08 Cr</t>
+            <t>4,363,636</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>436.36 Cr</t>
           </r>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1947,19 +1947,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,052,451</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>105.25 Cr</t>
+            <t>1,053,707</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.37 Cr</t>
           </r>
         </is>
       </c>
@@ -1970,19 +1970,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>356,035</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>35.60 Cr</t>
+            <t>357,291</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.73 Cr</t>
           </r>
         </is>
       </c>
@@ -1998,19 +1998,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>340,381</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>34.04 Cr</t>
+            <t>339,125</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.91 Cr</t>
           </r>
         </is>
       </c>
@@ -2107,19 +2107,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>528,378</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>52.84 Cr</t>
+            <t>529,510</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.95 Cr</t>
           </r>
         </is>
       </c>
@@ -2130,19 +2130,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>31,059</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.11 Cr</t>
+            <t>32,191</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.22 Cr</t>
           </r>
         </is>
       </c>
@@ -2158,19 +2158,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>466,260</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>46.63 Cr</t>
+            <t>465,128</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>46.51 Cr</t>
           </r>
         </is>
       </c>
@@ -2423,19 +2423,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,328,032</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1832.80 Cr</t>
+            <t>19,918,321</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1991.83 Cr</t>
           </r>
         </is>
       </c>
@@ -2446,25 +2446,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,030,096</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>203.01 Cr</t>
+            <t>3,620,384</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>362.04 Cr</t>
           </r>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2474,25 +2474,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>14,267,841</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1426.78 Cr</t>
+            <t>12,677,552</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1267.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -2583,19 +2583,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,591,631</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>159.16 Cr</t>
+            <t>1,591,127</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.11 Cr</t>
           </r>
         </is>
       </c>
@@ -2606,25 +2606,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,598,154</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>159.82 Cr</t>
+            <t>1,597,650</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-24402</t>
+          <t>-24394</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2634,25 +2634,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,604,676</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-160.47 Cr</t>
+            <t>-1,604,172</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-160.42 Cr</t>
           </r>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12201</t>
+          <t>-12197</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2866,19 +2866,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,689,447</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>368.94 Cr</t>
+            <t>3,689,125</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>368.91 Cr</t>
           </r>
         </is>
       </c>
@@ -2889,19 +2889,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>336,242</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.62 Cr</t>
+            <t>335,920</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.59 Cr</t>
           </r>
         </is>
       </c>
@@ -2917,19 +2917,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,016,962</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>301.70 Cr</t>
+            <t>3,017,284</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>301.73 Cr</t>
           </r>
         </is>
       </c>
@@ -3021,19 +3021,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,354,387</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>235.44 Cr</t>
+            <t>2,354,304</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>235.43 Cr</t>
           </r>
         </is>
       </c>
@@ -3044,19 +3044,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>304,160</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>30.42 Cr</t>
+            <t>304,078</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.41 Cr</t>
           </r>
         </is>
       </c>
@@ -3072,7 +3072,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,746,066</t>
+            <t>1,746,149</t>
           </r>
           <r>
             <t>
@@ -3331,7 +3331,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>405,401</t>
+            <t>405,373</t>
           </r>
           <r>
             <t>
@@ -3354,7 +3354,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>17,302</t>
+            <t>17,274</t>
           </r>
           <r>
             <t>
@@ -3382,7 +3382,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>370,797</t>
+            <t>370,825</t>
           </r>
           <r>
             <t>
@@ -3486,7 +3486,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>259,448</t>
+            <t>259,437</t>
           </r>
           <r>
             <t>
@@ -3509,7 +3509,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,144</t>
+            <t>11,132</t>
           </r>
           <r>
             <t>
@@ -3537,7 +3537,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>237,161</t>
+            <t>237,172</t>
           </r>
           <r>
             <t>
@@ -3641,7 +3641,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>437,059</t>
+            <t>437,090</t>
           </r>
           <r>
             <t>
@@ -3664,7 +3664,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>96,960</t>
+            <t>96,992</t>
           </r>
           <r>
             <t>
@@ -3692,7 +3692,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>243,138</t>
+            <t>243,107</t>
           </r>
           <r>
             <t>
@@ -3951,19 +3951,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>147,747</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.77 Cr</t>
+            <t>147,751</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.78 Cr</t>
           </r>
         </is>
       </c>
@@ -3974,7 +3974,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>42,790</t>
+            <t>42,794</t>
           </r>
           <r>
             <t>
@@ -4002,7 +4002,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>62,166</t>
+            <t>62,162</t>
           </r>
           <r>
             <t>
@@ -4106,7 +4106,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>318,467</t>
+            <t>318,453</t>
           </r>
           <r>
             <t>
@@ -4129,19 +4129,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>54,551</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.46 Cr</t>
+            <t>54,537</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.45 Cr</t>
           </r>
         </is>
       </c>
@@ -4157,7 +4157,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>209,365</t>
+            <t>209,379</t>
           </r>
           <r>
             <t>
@@ -4416,7 +4416,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>265,202</t>
+            <t>265,224</t>
           </r>
           <r>
             <t>
@@ -4439,7 +4439,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>111,162</t>
+            <t>111,184</t>
           </r>
           <r>
             <t>
@@ -4467,7 +4467,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>42,879</t>
+            <t>42,857</t>
           </r>
           <r>
             <t>
@@ -4726,19 +4726,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>8,335,181</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>833.52 Cr</t>
+            <t>8,334,780</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>833.48 Cr</t>
           </r>
         </is>
       </c>
@@ -4749,19 +4749,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,053,408</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>105.34 Cr</t>
+            <t>1,053,006</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.30 Cr</t>
           </r>
         </is>
       </c>
@@ -4777,19 +4777,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,228,366</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>622.84 Cr</t>
+            <t>6,228,767</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>622.88 Cr</t>
           </r>
         </is>
       </c>
@@ -4851,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -5009,19 +5009,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>862,766</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.28 Cr</t>
+            <t>1,005,406</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>100.54 Cr</t>
           </r>
         </is>
       </c>
@@ -5032,25 +5032,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>328,390</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.84 Cr</t>
+            <t>471,030</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>47.10 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>188</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -5060,25 +5060,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>205,986</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>20.60 Cr</t>
+            <t>63,346</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.33 Cr</t>
           </r>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -5164,19 +5164,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>79,644</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.96 Cr</t>
+            <t>84,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.49 Cr</t>
           </r>
         </is>
       </c>
@@ -5187,25 +5187,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,670</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.47 Cr</t>
+            <t>9,962</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5215,25 +5215,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>70,303</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.03 Cr</t>
+            <t>65,011</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.50 Cr</t>
           </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5319,19 +5319,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,011,062</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>201.11 Cr</t>
+            <t>2,320,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>232.08 Cr</t>
           </r>
         </is>
       </c>
@@ -5342,25 +5342,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>71,700</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.17 Cr</t>
+            <t>381,426</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.14 Cr</t>
           </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -5370,25 +5370,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,867,662</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>186.77 Cr</t>
+            <t>1,557,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>155.79 Cr</t>
           </r>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5474,19 +5474,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,013,588</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>201.36 Cr</t>
+            <t>2,025,688</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>202.57 Cr</t>
           </r>
         </is>
       </c>
@@ -5497,19 +5497,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>386,433</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.64 Cr</t>
+            <t>398,533</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.85 Cr</t>
           </r>
         </is>
       </c>
@@ -5525,19 +5525,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,240,722</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>124.07 Cr</t>
+            <t>1,228,622</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>122.86 Cr</t>
           </r>
         </is>
       </c>
@@ -5629,19 +5629,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,715,415</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>271.54 Cr</t>
+            <t>3,395,738</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>339.57 Cr</t>
           </r>
         </is>
       </c>
@@ -5652,25 +5652,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>363,737</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.37 Cr</t>
+            <t>1,044,060</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>104.41 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -5680,25 +5680,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,987,941</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>198.79 Cr</t>
+            <t>1,307,618</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>130.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5784,19 +5784,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>7,682,475</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>768.25 Cr</t>
+            <t>8,832,556</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>883.26 Cr</t>
           </r>
         </is>
       </c>
@@ -5807,25 +5807,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,154,930</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>115.49 Cr</t>
+            <t>2,305,012</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>230.50 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5835,25 +5835,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,372,614</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>537.26 Cr</t>
+            <t>4,222,533</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>422.25 Cr</t>
           </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -5907,7 +5907,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 25.09.2026</t>
+          <t>Open Line FR Report - As On 05.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6019,19 +6019,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>81,555</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.16 Cr</t>
+            <t>80,418</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.04 Cr</t>
           </r>
         </is>
       </c>
@@ -6042,25 +6042,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-79,348</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-7.93 Cr</t>
+            <t>-80,485</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-8.05 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -6110,19 +6110,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>12,767</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.28 Cr</t>
+            <t>12,890</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.29 Cr</t>
           </r>
         </is>
       </c>
@@ -6133,25 +6133,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-19,460</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-1.95 Cr</t>
+            <t>-19,337</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.93 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -6201,7 +6201,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>64,676</t>
+            <t>64,681</t>
           </r>
           <r>
             <t>
@@ -6224,7 +6224,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-55,642</t>
+            <t>-55,637</t>
           </r>
           <r>
             <t>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>53.76</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -6292,19 +6292,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>379,202</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.92 Cr</t>
+            <t>379,598</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.96 Cr</t>
           </r>
         </is>
       </c>
@@ -6315,25 +6315,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-128,218</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-12.82 Cr</t>
+            <t>-127,822</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-12.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>74.81</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -6383,19 +6383,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,805,865</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>380.59 Cr</t>
+            <t>4,286,712</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>428.67 Cr</t>
           </r>
         </is>
       </c>
@@ -6406,25 +6406,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>843,070</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>84.31 Cr</t>
+            <t>1,323,917</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>132.39 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>128.46</t>
+          <t>144.68</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -6474,19 +6474,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>183,938</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>18.39 Cr</t>
+            <t>187,787</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.78 Cr</t>
           </r>
         </is>
       </c>
@@ -6497,25 +6497,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>51,671</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.17 Cr</t>
+            <t>55,520</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.55 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>139.07</t>
+          <t>141.98</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -6565,19 +6565,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>140,407</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.04 Cr</t>
+            <t>251,247</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>25.12 Cr</t>
           </r>
         </is>
       </c>
@@ -6588,25 +6588,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-382,436</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-38.24 Cr</t>
+            <t>-271,596</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-27.16 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -6838,19 +6838,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>25,991</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.60 Cr</t>
+            <t>29,430</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.94 Cr</t>
           </r>
         </is>
       </c>
@@ -6861,25 +6861,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-14,381</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-1.44 Cr</t>
+            <t>-10,942</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.09 Cr</t>
           </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>64.38</t>
+          <t>72.90</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -7020,19 +7020,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>71,111</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.11 Cr</t>
+            <t>72,216</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.22 Cr</t>
           </r>
         </is>
       </c>
@@ -7043,25 +7043,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-26,389</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-2.64 Cr</t>
+            <t>-25,284</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-2.53 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>72.93</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -7111,19 +7111,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>147,126</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.71 Cr</t>
+            <t>155,585</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.56 Cr</t>
           </r>
         </is>
       </c>
@@ -7134,25 +7134,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-163,786</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-16.38 Cr</t>
+            <t>-155,327</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-15.53 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -7293,19 +7293,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>112,585</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.26 Cr</t>
+            <t>113,720</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.37 Cr</t>
           </r>
         </is>
       </c>
@@ -7316,25 +7316,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-203,148</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-20.31 Cr</t>
+            <t>-202,013</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.20 Cr</t>
           </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -7558,19 +7558,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,135,999</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>513.60 Cr</t>
+            <t>5,745,060</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>574.51 Cr</t>
           </r>
         </is>
       </c>
@@ -7581,25 +7581,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-498,880</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-49.89 Cr</t>
+            <t>110,181</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.02 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>91.15</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -7635,7 +7635,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 25.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 05.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -7742,19 +7742,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>457,028</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>45.70 Cr</t>
+            <t>494,859</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>49.49 Cr</t>
           </r>
         </is>
       </c>
@@ -7765,30 +7765,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>588,503</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>58.85 Cr</t>
+            <t>550,672</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>55.07 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>56.29</t>
+          <t>52.67</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -7833,19 +7833,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>21,238</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.12 Cr</t>
+            <t>22,085</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.21 Cr</t>
           </r>
         </is>
       </c>
@@ -7856,30 +7856,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,994</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.90 Cr</t>
+            <t>18,147</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.81 Cr</t>
           </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>52.79</t>
+          <t>54.89</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -8106,19 +8106,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,844,908</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>384.49 Cr</t>
+            <t>4,324,735</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>432.47 Cr</t>
           </r>
         </is>
       </c>
@@ -8129,30 +8129,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-727,393</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-72.74 Cr</t>
+            <t>-1,207,220</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-120.72 Cr</t>
           </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>123.33</t>
+          <t>138.72</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-38.72</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -8288,19 +8288,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>794,366</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>79.44 Cr</t>
+            <t>884,922</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>88.49 Cr</t>
           </r>
         </is>
       </c>
@@ -8311,30 +8311,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>506,643</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>50.66 Cr</t>
+            <t>416,087</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>41.61 Cr</t>
           </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2708,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4851,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2708,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4851,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - SEP 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - SEP 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - SE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 19." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -5907,7 +5907,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 05.10.2026</t>
+          <t>Open Line FR Report - As On 19.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6019,19 +6019,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>80,418</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.04 Cr</t>
+            <t>99,183</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.92 Cr</t>
           </r>
         </is>
       </c>
@@ -6042,25 +6042,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-80,485</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-8.05 Cr</t>
+            <t>-61,720</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-6.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -6110,19 +6110,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>12,890</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.29 Cr</t>
+            <t>13,774</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.38 Cr</t>
           </r>
         </is>
       </c>
@@ -6133,25 +6133,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-19,337</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-1.93 Cr</t>
+            <t>-18,453</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -6292,19 +6292,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>379,598</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.96 Cr</t>
+            <t>398,602</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.86 Cr</t>
           </r>
         </is>
       </c>
@@ -6315,25 +6315,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-127,822</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-12.78 Cr</t>
+            <t>-108,818</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-10.88 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>74.81</t>
+          <t>78.55</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -6383,19 +6383,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,286,712</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>428.67 Cr</t>
+            <t>4,376,267</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>437.63 Cr</t>
           </r>
         </is>
       </c>
@@ -6406,25 +6406,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,323,917</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>132.39 Cr</t>
+            <t>1,413,472</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>141.35 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>144.68</t>
+          <t>147.71</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -6474,19 +6474,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>187,787</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>18.78 Cr</t>
+            <t>187,876</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.79 Cr</t>
           </r>
         </is>
       </c>
@@ -6497,25 +6497,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>55,520</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.55 Cr</t>
+            <t>55,609</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.56 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>141.98</t>
+          <t>142.04</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -6565,19 +6565,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>251,247</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>25.12 Cr</t>
+            <t>307,683</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.77 Cr</t>
           </r>
         </is>
       </c>
@@ -6588,25 +6588,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-271,596</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-27.16 Cr</t>
+            <t>-215,160</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.52 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>58.85</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -6656,19 +6656,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>105,095</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>10.51 Cr</t>
+            <t>107,120</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.71 Cr</t>
           </r>
         </is>
       </c>
@@ -6679,25 +6679,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-202,748</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-20.27 Cr</t>
+            <t>-200,723</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.07 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>34.80</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -6929,19 +6929,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,681</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.57 Cr</t>
+            <t>8,185</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.82 Cr</t>
           </r>
         </is>
       </c>
@@ -6952,25 +6952,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-48,021</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.80 Cr</t>
+            <t>-45,517</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.55 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -7020,19 +7020,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>72,216</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.22 Cr</t>
+            <t>79,886</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.99 Cr</t>
           </r>
         </is>
       </c>
@@ -7043,25 +7043,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-25,284</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-2.53 Cr</t>
+            <t>-17,614</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>81.93</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -7111,19 +7111,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>155,585</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>15.56 Cr</t>
+            <t>209,920</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>20.99 Cr</t>
           </r>
         </is>
       </c>
@@ -7134,25 +7134,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-155,327</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-15.53 Cr</t>
+            <t>-100,992</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-10.10 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>67.52</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -7293,19 +7293,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>113,720</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.37 Cr</t>
+            <t>124,015</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.40 Cr</t>
           </r>
         </is>
       </c>
@@ -7316,25 +7316,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-202,013</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-20.20 Cr</t>
+            <t>-191,718</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-19.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -7558,19 +7558,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,745,060</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>574.51 Cr</t>
+            <t>6,006,622</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>600.66 Cr</t>
           </r>
         </is>
       </c>
@@ -7581,25 +7581,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>110,181</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.02 Cr</t>
+            <t>371,743</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>106.60</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -7635,7 +7635,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 05.10.2026</t>
+          <t>Open Line FR Fund Wise - As On 19.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -7742,19 +7742,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>494,859</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>49.49 Cr</t>
+            <t>621,086</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>62.11 Cr</t>
           </r>
         </is>
       </c>
@@ -7765,30 +7765,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>550,672</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>55.07 Cr</t>
+            <t>424,445</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>42.44 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>59.40</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>52.67</t>
+          <t>40.60</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -7833,19 +7833,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>22,085</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.21 Cr</t>
+            <t>25,605</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.56 Cr</t>
           </r>
         </is>
       </c>
@@ -7856,30 +7856,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,147</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.81 Cr</t>
+            <t>14,627</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.46 Cr</t>
           </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>54.89</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -7924,19 +7924,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,459</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.85 Cr</t>
+            <t>18,607</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.86 Cr</t>
           </r>
         </is>
       </c>
@@ -7947,30 +7947,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>112,133</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.21 Cr</t>
+            <t>111,985</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.20 Cr</t>
           </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>85.87</t>
+          <t>85.75</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -8106,19 +8106,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,324,735</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>432.47 Cr</t>
+            <t>4,405,363</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>440.54 Cr</t>
           </r>
         </is>
       </c>
@@ -8129,30 +8129,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,207,220</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-120.72 Cr</t>
+            <t>-1,287,848</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-128.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>138.72</t>
+          <t>141.31</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-38.72</t>
+          <t>-41.31</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -8288,19 +8288,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>884,922</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>88.49 Cr</t>
+            <t>935,961</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>93.60 Cr</t>
           </r>
         </is>
       </c>
@@ -8311,30 +8311,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>416,087</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>41.61 Cr</t>
+            <t>365,048</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.50 Cr</t>
           </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>71.94</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>28.06</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -621,19 +621,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>641,522</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>64.15 Cr</t>
+            <t>643,222</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>64.32 Cr</t>
           </r>
         </is>
       </c>
@@ -644,19 +644,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>320,761</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.08 Cr</t>
+            <t>321,611</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.16 Cr</t>
           </r>
         </is>
       </c>
@@ -690,19 +690,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,751</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.28 Cr</t>
+            <t>31,901</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.19 Cr</t>
           </r>
         </is>
       </c>
@@ -718,19 +718,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>288,010</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>28.80 Cr</t>
+            <t>289,710</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.97 Cr</t>
           </r>
         </is>
       </c>
@@ -781,19 +781,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,608,902</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>360.89 Cr</t>
+            <t>3,809,302</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>380.93 Cr</t>
           </r>
         </is>
       </c>
@@ -804,19 +804,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,804,451</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>180.45 Cr</t>
+            <t>1,904,651</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>190.47 Cr</t>
           </r>
         </is>
       </c>
@@ -850,25 +850,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>321,923</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.19 Cr</t>
+            <t>221,723</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>22.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -878,25 +878,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,482,528</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>148.25 Cr</t>
+            <t>1,682,928</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>168.29 Cr</t>
           </r>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1261,19 +1261,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,059,950</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>206.00 Cr</t>
+            <t>2,111,950</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>211.19 Cr</t>
           </r>
         </is>
       </c>
@@ -1284,19 +1284,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,029,975</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>103.00 Cr</t>
+            <t>1,055,975</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.60 Cr</t>
           </r>
         </is>
       </c>
@@ -1330,25 +1330,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>162,435</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>16.24 Cr</t>
+            <t>136,435</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.64 Cr</t>
           </r>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1358,25 +1358,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>867,540</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.75 Cr</t>
+            <t>919,540</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>91.95 Cr</t>
           </r>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1581,19 +1581,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,428,766</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>442.88 Cr</t>
+            <t>4,504,666</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>450.47 Cr</t>
           </r>
         </is>
       </c>
@@ -1604,19 +1604,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,214,383</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>221.44 Cr</t>
+            <t>2,252,333</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>225.23 Cr</t>
           </r>
         </is>
       </c>
@@ -1650,25 +1650,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>388,218</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.82 Cr</t>
+            <t>350,268</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.03 Cr</t>
           </r>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1678,25 +1678,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,826,165</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>182.62 Cr</t>
+            <t>1,902,065</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>190.21 Cr</t>
           </r>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2377,19 +2377,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,595,873</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3259.59 Cr</t>
+            <t>32,925,873</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3292.59 Cr</t>
           </r>
         </is>
       </c>
@@ -2400,19 +2400,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,297,936</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1629.79 Cr</t>
+            <t>16,462,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1646.29 Cr</t>
           </r>
         </is>
       </c>
@@ -2446,25 +2446,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,620,384</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>362.04 Cr</t>
+            <t>3,455,384</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>345.54 Cr</t>
           </r>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2474,25 +2474,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>12,677,552</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1267.76 Cr</t>
+            <t>13,007,552</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1300.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>PU Wise - Staff - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4851,7 +4851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -5118,19 +5118,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>149,947</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.99 Cr</t>
+            <t>192,347</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>19.23 Cr</t>
           </r>
         </is>
       </c>
@@ -5141,19 +5141,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>74,974</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.50 Cr</t>
+            <t>96,174</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.62 Cr</t>
           </r>
         </is>
       </c>
@@ -5187,25 +5187,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>9,962</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.00 Cr</t>
+            <t>-11,238</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.12 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5215,25 +5215,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>65,011</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>6.50 Cr</t>
+            <t>107,411</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.74 Cr</t>
           </r>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5428,19 +5428,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,254,310</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>325.43 Cr</t>
+            <t>3,541,910</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>354.19 Cr</t>
           </r>
         </is>
       </c>
@@ -5451,19 +5451,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,627,155</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>162.72 Cr</t>
+            <t>1,770,955</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>177.10 Cr</t>
           </r>
         </is>
       </c>
@@ -5497,25 +5497,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>398,533</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>39.85 Cr</t>
+            <t>254,733</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>25.47 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -5525,25 +5525,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,228,622</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>122.86 Cr</t>
+            <t>1,516,222</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>151.62 Cr</t>
           </r>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -5738,19 +5738,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>13,055,089</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1305.51 Cr</t>
+            <t>13,385,089</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1338.51 Cr</t>
           </r>
         </is>
       </c>
@@ -5761,19 +5761,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,527,544</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>652.75 Cr</t>
+            <t>6,692,544</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>669.25 Cr</t>
           </r>
         </is>
       </c>
@@ -5807,25 +5807,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,305,012</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>230.50 Cr</t>
+            <t>2,140,012</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>214.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5835,25 +5835,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,222,533</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>422.25 Cr</t>
+            <t>4,552,533</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>455.25 Cr</t>
           </r>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
